--- a/光伏配储项目/电价数据/2026/成田站.xlsx
+++ b/光伏配储项目/电价数据/2026/成田站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.32013</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.43724</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.32143</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.31706</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.31771</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.3166600000000001</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.3136</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.31662</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.32174</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.32273</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.32263</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.28289</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.27783</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.28699</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.27751</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.28822</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.26652</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.25914</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.19311</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.19445</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.2061</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.27742</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.30946</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07246999999999999</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.1274</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17018</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26354</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25147</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.2561</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24075</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.23257</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.30891</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.27845</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.30239</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.20625</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.44869</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.46723</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.05815</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.7459199999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.35151</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.45097</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.6264500000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.27396</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.12679</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.96413</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.04402</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.04308</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.9065700000000001</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.20339</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.4565</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5268400000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5425800000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.16643</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.5198200000000001</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.47577</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.5314</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.42146</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.34423</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.34584</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.42923</v>
+      </c>
+      <c r="D118" t="n">
+        <v>0.6540499999999999</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.45371</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.58477</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.45802</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.35679</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.36033</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.3584</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.35904</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.34586</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32242</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32461</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.32736</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.35821</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.34145</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.33828</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.32619</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.33823</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.36249</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.32674</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.32472</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.34552</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.2781</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.20019</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.26977</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.64885</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.60933</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.46322</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.29082</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34186</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.31737</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.31085</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.27853</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.23933</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.16371</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.35579</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.27356</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.37742</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.41664</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.42263</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.24332</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.88498</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.9875700000000001</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.87141</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.47573</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.89789</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.9071</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.96282</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.03797</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.89158</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.62374</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.84773</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.50485</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.8686799999999999</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.8138300000000001</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.8750599999999999</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.5885900000000001</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.06383</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.34918</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.5838</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5114300000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.33514</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.32775</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.33875</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.31903</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.32023</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.31999</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.33484</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.35443</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.38449</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.33348</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.33613</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.12524</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.17349</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.24102</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.07235999999999999</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.39667</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.29339</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.40549</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.41564</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.73017</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.76207</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.79372</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.43187</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.27197</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.37712</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.49863</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.40617</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.15222</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45844</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51162</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.51485</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.52986</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.56956</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.55048</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.62905</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.59739</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70713</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.43462</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50429</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.53228</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.52446</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.66747</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.54965</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.41214</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.60268</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.37595</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.40923</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.4071</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.53852</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.46489</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.57453</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.53716</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.48084</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48195</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.54573</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.36986</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.33339</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.3694</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.33614</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.33129</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.33194</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3229</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.32306</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.32187</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.32469</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33639</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.33582</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.34533</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.37926</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44533</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37651</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.3281</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.34458</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35824</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32771</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.42408</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48555</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46821</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.379</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.11773</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29657</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.79902</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.16542</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.16099</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.31815</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.20007</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.3541</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31765</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.3678</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.0721</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.38027</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.26831</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.25749</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.06920999999999999</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.19103</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45063</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.41739</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.44218</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.66999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.39479</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.35886</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50242</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.31261</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.30701</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.30681</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.30364</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.2746499999999999</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.06216</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36469</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.36441</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34018</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32794</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30817</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30062</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28971</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.31143</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14366</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02664</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29146</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.2977</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40534</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.3439</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26375</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.2564</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.2385</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10316</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.29842</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.26191</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.02756</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.2635</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33781</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34795</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.3395899999999999</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.35034</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34811</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36312</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36746</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.41887</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35642</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.42689</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35173</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31889</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.1628</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.30805</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.25104</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25594</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.10026</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.14474</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.29133</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19849</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.05027</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.01486</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25407</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.04403</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.13684</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.0684</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.25228</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.22085</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19913</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.04832</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.18149</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.2536</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27452</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20822</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26955</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01017</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20649</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04941</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27584</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19394</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.30991</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.01218</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06064</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05885</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.32738</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.32556</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31674</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30348</v>
+      </c>
+      <c r="C123" t="n">
+        <v>0.84241</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31936</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.3236</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.13456</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.77427</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8704</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6596000000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5743400000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.42406</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.40952</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39999</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44402</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.41011</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.48848</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.58673</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.35833</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29599</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.44685</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.43483</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.33911</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.65567</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26764</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.37273</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.37759</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.24879</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32118</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30625</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.32983</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28662</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31576</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29378</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.2957</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30569</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.18621</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26479</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.2647</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.2790899999999999</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26458</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28321</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32588</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31181</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30971</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29525</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30814</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30785</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30886</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29443</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32504</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.80163</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.3155</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.3127</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30666</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.30463</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30926</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29664</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29785</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.22997</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.23382</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.30012</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.2854</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.13167</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.05029</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29304</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.1293</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30404</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.05194</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31217</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.08125</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.14099</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.0517</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.37775</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.10255</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.44787</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.15691</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.05164</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.06661</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.02879</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.08222</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.04803</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.05882</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.06083</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.04621</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>-0.00182</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.04241</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.03721</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>-0.0027</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.04492</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.04031000000000001</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>-0.0367</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>-0.00967</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>-0.02794</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.12255</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.05926</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.04277</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.05805</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.05313</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.05839</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.06586</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.04653</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.05578</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.05678</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.05884</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.05098</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.05824</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.05923</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.06315999999999999</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.06224</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.05903</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.13343</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.05888</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.09358</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.06472</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.08663999999999999</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.05534</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.06677</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.24126</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.05954</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.05798</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.06257</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.02582</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.17159</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.26811</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.08256000000000001</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.13673</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.12553</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.12109</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.03298</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.02779</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.07779000000000001</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.09198000000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.08428000000000001</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.06633</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.07081</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.15735</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.06902</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.14386</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.10053</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.17216</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.00278</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.17441</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.26535</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>-0.02591</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.08906</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.25173</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.27017</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.20478</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>-0.04889</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.25064</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.12596</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.20211</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.25459</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.30022</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.04952</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.08762</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.04459</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.29106</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.25404</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.29173</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.25973</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.01422</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.22595</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.10183</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.17803</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.0353</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.10079</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.20918</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.07725</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.10115</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.08968000000000001</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.13407</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.15468</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.0426</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.10212</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.21938</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.10722</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.25612</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.26284</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.04988</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.26607</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.10007</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.11997</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.14899</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.1455</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.1419</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.14461</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.13533</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.11677</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.16068</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.13908</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.12242</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.16232</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.14268</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.14153</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.26106</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.06697</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.14359</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.29617</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.16091</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.13588</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.25065</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.11462</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.24233</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.04346</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.11826</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.10739</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.08362</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.01759</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.08477999999999999</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19453</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.07192</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.19166</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.05874</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.09572</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.10678</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.10492</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.12316</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="R127" t="n">
+        <v>-0.0032</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.00697</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.0927</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.09904</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.11911</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.03351</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.00334</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.19797</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.03413</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.06355</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.06217</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.07417</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.11371</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.20086</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.07848000000000001</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.17295</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.06139</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.25804</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>-0.02824</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.02824</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.02747</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>-0.00311</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.15641</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.09576000000000001</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.09681000000000001</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.28409</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.15153</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.25188</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.10598</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.15465</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.09827</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.0945</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.18863</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.20487</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25123</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.22849</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.26863</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.2473</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.26516</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.22016</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.24529</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.26914</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.25812</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.24371</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.2786</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.26854</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.2779</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29882</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3048</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28498</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28771</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.30131</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30264</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.31082</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.28163</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.28121</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.28999</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.28079</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.28195</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.39793</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.29246</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.28848</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.32963</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28818</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.29044</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25429</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28478</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29201</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.3147</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30241</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3057</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34227</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33449</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30944</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.3062</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30223</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30235</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29788</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29827</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.30859</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29955</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30495</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30313</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30314</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29351</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29638</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29226</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.31004</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33218</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28305</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.28876</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30366</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28554</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.30908</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28352</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.2548</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30195</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28884</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29556</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.2898</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27939</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29939</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31498</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30147</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.3054</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30907</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29522</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31102</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24378</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28809</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30445</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.29239</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32929</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38383</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.43771</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.30673</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.35671</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32512</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.36094</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.3169</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31675</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.31077</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.31118</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30634</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32067</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.30962</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33784</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31523</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29665</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30219</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29807</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31467</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.31145</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29863</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29884</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31314</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.39986</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.02286</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.4159</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6408200000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.39111</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.48333</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49467</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.38302</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43574</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.49246</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.3894</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.4291</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.54764</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27851</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.35224</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.27515</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.23787</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.50064</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.26303</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.2506</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.44264</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.42065</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.40616</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.53804</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.43237</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.43703</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.18833</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.16999</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.33886</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.10172</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.1625</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.44645</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42994</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.10369</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.21945</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6476799999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38586</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.15373</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34608</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47223</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.03478</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.09042</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.12295</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.12722</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32097</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.2573</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.03062</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28845</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.04203</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.03088</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.18889</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.27705</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27792</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28134</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28193</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20669</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.1986</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27228</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27128</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27118</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27691</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.20048</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.19778</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.16322</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23991</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.2799</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.20038</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.00083</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19751</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.20316</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.06576</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.21039</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17686</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16789</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.18233</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.21448</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.25228</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.24399</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.27506</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.26036</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.30422</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.25623</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.00141</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.257</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.24303</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.2658</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.2437</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.23762</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.22866</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.2152</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.25294</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.24073</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.27988</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.25242</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.22151</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.2174</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.11615</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.20915</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.2197</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.01918</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.24626</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.28371</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.2015</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.26718</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.28851</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.24509</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.27278</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.30876</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.30661</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.27697</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.29119</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31783</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.28163</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27873</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.23407</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29445</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.21921</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.28101</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.32131</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.05116</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.0535</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.24069</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.31946</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29505</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32173</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28448</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31794</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.00408</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31872</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29228</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28897</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27712</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31127</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28853</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.2878500000000001</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29607</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28599</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.2872</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27666</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28698</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29298</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.28365</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27706</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28755</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29544</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27715</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28748</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27252</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30109</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31686</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30201</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3065</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31047</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32151</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32231</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30512</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32246</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34352</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32175</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32953</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3361</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.33247</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39718</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.5762200000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.54931</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.21507</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.33592</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29931</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38284</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34798</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33372</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31767</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33067</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32453</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33758</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32826</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30912</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41491</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31921</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32066</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.3265</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32402</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.31922</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33937</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33859</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32696</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.41669</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37343</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39301</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32353</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.37685</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.45858</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.50596</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6066699999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.57089</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.61885</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.75525</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.43682</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.39546</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.47636</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40377</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.43596</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35613</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32342</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31675</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.33796</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.32124</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32593</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32514</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36642</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.33116</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31645</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.29354</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.3087</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.30063</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.29133</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30548</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.45243</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.35243</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42871</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.36541</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37507</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31931</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.36447</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35596</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.3414700000000001</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.3489</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.006059999999999999</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.27595</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.34971</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32553</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.28465</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.24215</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.31174</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.3097</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.23514</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.28464</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.31033</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.30384</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.31692</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.31403</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.31238</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.31927</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.31459</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.33273</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.32968</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.5472899999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64418</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.32629</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.32445</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40618</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38784</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.27664</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29297</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31736</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.3319</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.01822</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28799</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.28182</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.2888</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29553</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.28608</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.2323</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37115</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.28582</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.30556</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.30183</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.25312</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.12359</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.2743</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.08762</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03215999999999999</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39016</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.00107</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>-0.04886</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>-0.03890999999999999</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.2095</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>-0.03795</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>-0.01369</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.0196</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.31239</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.00301</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>-0.03611</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>-0.04336</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>-0.01806</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.20758</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.21762</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.2159</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.2194</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>-0.02147</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.30332</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.28667</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.22009</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.26003</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.02917</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.20625</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37981</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.07399</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.04497</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.04155</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.04715</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.12372</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.10443</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.05139</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.29857</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.19881</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>-0.04906</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.02282</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.02573</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.00248</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>-0.02678</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.03251</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.02985</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.03413</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.13575</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.29344</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.21175</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.15478</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.20004</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.28321</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.2084</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.17671</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.01706</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.25002</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.01319</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.01347</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.17692</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.00282</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20789</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.27965</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17574</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.01201</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.16587</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.00196</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.00186</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.16814</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.17097</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.1738</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.01092</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17663</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.01073</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.01304</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18915</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.15803</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.24042</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.03222</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.26235</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.10387</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.21977</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.14308</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.17376</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.27132</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.07248</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.28918</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.25673</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.22165</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.19377</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.00268</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.07814</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.04075</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>-0.00181</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.03149</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.24627</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.23191</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.17883</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.08855</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.03126</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.05905</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.03990999999999999</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.04918</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.04537</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.05194</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.07543999999999999</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.07789</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.1871</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.18792</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.04755</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.00617</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.23002</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.19262</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.17593</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>-0.04993</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.09637999999999999</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.16719</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.19573</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.07733</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.03403</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.09292</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.07625</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.03793999999999999</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22717</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.12539</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.06695000000000001</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25288</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.08404</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.22991</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.23699</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.23412</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.11922</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.12993</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.23722</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.10141</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.22364</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.06301</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.07214</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.19922</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.23447</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.24651</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.25971</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.2819700000000001</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27648</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.05651</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.19184</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18878</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26916</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.00242</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20746</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21945</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.04522</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.00842</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.00466</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.00465</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.00405</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.00405</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.00441</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.20217</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.00898</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.00405</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.004099999999999999</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.18257</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.008410000000000001</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.00842</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.005730000000000001</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.00069</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24597</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.03954</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00597</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00035</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>-0.00451</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02202</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.03481</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04399</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.03791</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.23712</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04955</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04633</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.12416</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.21971</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.22636</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.22812</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22552</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22933</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.00536</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.21289</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.25766</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31036</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.2962</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30371</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.26788</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29706</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.26208</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.23888</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.30328</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.28937</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.29859</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.30138</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3036</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.24092</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.30078</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27338</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.03942</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28603</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.31121</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.28434</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.17954</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.17394</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.17843</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.1757</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.01566</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.17165</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.16008</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.01464</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.04558</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.0437</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.01738</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.0142</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.04983</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.01303</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.0154</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.01959</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.20313</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.20132</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>-0.04905</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.04439</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.04712</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.03579</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85097</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86168</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09322</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.00341</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.2517</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31386</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31854</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28019</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29739</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.45632</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29751</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00225</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00157</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32064</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06873</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30695</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47495</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32727</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33432</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32518</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33594</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.68867</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.51798</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.38835</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.44299</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.7692899999999999</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.85438</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.5828300000000001</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.44781</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.67777</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.72934</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.72756</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.73092</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.81088</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.44201</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32114</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.34992</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31154</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.31138</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.44577</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.3168</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.27848</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.27142</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.20186</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.26386</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25936</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.25243</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.22201</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.272</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.20995</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.17689</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20541</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.17115</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.17394</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.0162</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.17007</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.19229</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.24073</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.29437</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.24925</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.25905</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29935</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25733</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32549</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38276</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33096</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29673</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30752</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25848</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30236</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32037</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31805</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31677</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31171</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.31847</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.31966</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33589</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37408</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33774</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32501</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.31475</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29947</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.2953</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.35326</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32223</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32789</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30488</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29704</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30282</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.3029</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31599</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31538</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31614</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.34956</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.33413</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.16394</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.33094</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33529</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33425</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29667</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32431</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32105</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32954</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33316</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.45449</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41459</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.45038</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.27721</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.73691</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.77619</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.4134</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.44328</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5127999999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.67274</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.7738700000000001</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.42211</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.38787</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.35026</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35749</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33446</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.33059</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.20366</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.31067</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31951</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38889</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34734</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31613</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.32058</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31721</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31853</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31813</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30809</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30277</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30725</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30253</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29714</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30798</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.31319</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30714</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33842</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36256</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43461</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35645</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.36928</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.35797</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33681</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.35533</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.35141</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37288</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38848</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.3752</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.36786</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.36962</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.46134</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.61651</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.40637</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.40549</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.36768</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.39891</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7435</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.65547</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5647300000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.34454</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.40109</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.34177</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3241</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28528</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33255</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28746</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29915</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29285</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.30199</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32541</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29288</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32528</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31457</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30439</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30473</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.01631</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29119</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28715</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31585</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28635</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3578</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35842</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33612</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30772</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30604</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31252</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32239</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32733</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.38263</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.32323</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.27354</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.4347200000000001</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.34751</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.39927</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.34789</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.20054</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43563</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.5485800000000001</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.34651</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.3225</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34838</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33579</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34611</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.3518</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.18404</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34679</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.35834</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.32882</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.21736</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.47893</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.35223</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37223</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.34636</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36151</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35978</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.34232</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.34239</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.33038</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32834</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.6761699999999999</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.42074</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.41356</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.36575</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34281</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33829</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.34002</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34469</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3394</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33909</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.3395</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32981</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33362</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.33476</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32308</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3322</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3405899999999999</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32667</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32693</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.34055</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33971</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.3335</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34787</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.29823</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.3162</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.32653</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.18872</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30291</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.2787</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.30757</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.31151</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30572</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.31543</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.33919</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.07775</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.07537999999999999</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.22435</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.02819</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.3444</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35313</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38214</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.23743</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.15209</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.37747</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36226</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.35942</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.35981</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33641</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3399</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="E143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F143" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.23047</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.33048</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33325</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33336</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34312</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33736</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33483</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33708</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32668</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33143</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30601</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30987</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17607</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30464</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14573</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19862</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14601</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2876</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04754</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12155</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33321</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22594</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26023</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14405</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14523</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18828</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.2767</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.03338</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.00409</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.22822</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.01147</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.14176</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.22897</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.06731999999999999</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>-0.01075</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.22237</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.15126</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.24723</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.28354</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.23455</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>-0.0269</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>-0.02559</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.1875</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.16247</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.10526</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.27868</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.42589</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.25428</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.07174999999999999</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.02245</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>-0.03736</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.02621</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.06852</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.28586</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.09353</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.07948000000000001</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.34052</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.33424</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.34126</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38656</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.3538</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.34481</v>
       </c>
     </row>
   </sheetData>
